--- a/sheets/대금율보/검수/꽃길.xlsx
+++ b/sheets/대금율보/검수/꽃길.xlsx
@@ -5523,7 +5523,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
+          <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
+          <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
@@ -5563,7 +5563,7 @@
       <c r="K5" s="23"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
+          <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
@@ -5771,7 +5771,7 @@
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無)
-林‹</t>
+林</t>
         </is>
       </c>
       <c r="Q7" s="22" t="inlineStr">
@@ -5782,7 +5782,7 @@
       <c r="R7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無)
-林‹</t>
+林</t>
         </is>
       </c>
       <c r="S7" s="27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
-–林‹</t>
+–林</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -6174,7 +6174,7 @@
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
-–林‹</t>
+–林</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -6191,7 +6191,7 @@
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
-–林‹</t>
+–林</t>
         </is>
       </c>
       <c r="M13" s="23" t="inlineStr">
@@ -6719,8 +6719,8 @@
       <c r="S24" s="24"/>
       <c r="T24" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢?
-無?</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="U24" s="30"/>

--- a/sheets/대금율보/검수/꽃길.xlsx
+++ b/sheets/대금율보/검수/꽃길.xlsx
@@ -5328,32 +5328,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="104.04" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="104.04" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="104.04" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="104.04" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="U6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="104.04" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="25" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="104.04" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -5855,7 +5855,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="104.04" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -5900,7 +5900,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="104.04" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="104.04" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="104.04" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="104.04" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -6235,7 +6235,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="104.04" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="104.04" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="U15" s="27"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="104.04" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="104.04" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="104.04" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6590,10 +6590,10 @@
       </c>
       <c r="U18" s="26"/>
     </row>
-    <row r="19">
+    <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="93.02" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="104.04" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="104.04" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="23"/>
@@ -6670,7 +6670,7 @@
       <c r="T22" s="21"/>
       <c r="U22" s="23"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="104.04" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="23"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="U23" s="23"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="104.04" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="24"/>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="U24" s="30"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="104.04" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="U25" s="27"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="104.04" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="23"/>
@@ -6775,7 +6775,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="104.04" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -6798,7 +6798,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="104.04" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="U28" s="26"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="104.04" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -6848,7 +6848,7 @@
       <c r="T29" s="21"/>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="104.04" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="23"/>
@@ -6871,7 +6871,7 @@
       <c r="T30" s="21"/>
       <c r="U30" s="23"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="104.04" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="23"/>
@@ -6894,7 +6894,7 @@
       <c r="T31" s="21"/>
       <c r="U31" s="23"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="104.04" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="24"/>
@@ -6917,7 +6917,7 @@
       <c r="T32" s="21"/>
       <c r="U32" s="24"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="104.04" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -6940,7 +6940,7 @@
       <c r="T33" s="21"/>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="104.04" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="23"/>
@@ -6963,7 +6963,7 @@
       <c r="T34" s="21"/>
       <c r="U34" s="23"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="104.04" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -6986,7 +6986,7 @@
       <c r="T35" s="21"/>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="104.04" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -7016,7 +7016,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="16383" man="1"/>
   </rowBreaks>
